--- a/data/Measurer_metadata_tracking.xlsx
+++ b/data/Measurer_metadata_tracking.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288AA8A3-7AA7-984F-A63D-7779A4562EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785D460A-B1D6-FB45-ABAB-8BA2D87F66EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="500" windowWidth="28040" windowHeight="16280" xr2:uid="{9CDA16BA-74DE-1D48-B98F-7FC82E70CC92}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="28040" windowHeight="15940" xr2:uid="{9CDA16BA-74DE-1D48-B98F-7FC82E70CC92}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="217">
   <si>
     <t>Sr. No</t>
   </si>
@@ -172,9 +172,6 @@
     <t>Y (for both)</t>
   </si>
   <si>
-    <t>Data collection for bulbuls complete</t>
-  </si>
-  <si>
     <t>cprobst@umich.edu</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>PM, MH, MB</t>
   </si>
   <si>
-    <t>KU (Kansas University</t>
-  </si>
-  <si>
     <t>cgmeneses23@ku.edu</t>
   </si>
   <si>
@@ -235,9 +229,6 @@
     <t xml:space="preserve">petomikula158@gmail.com, bulla.mar@gmail.com </t>
   </si>
   <si>
-    <t>He mentioned he would follow up on the preliminary dataset on 30th March, should remind again</t>
-  </si>
-  <si>
     <t>VUW (Victoria University of Wellington)</t>
   </si>
   <si>
@@ -274,9 +265,6 @@
     <t>Klara Widrig</t>
   </si>
   <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>NMNH Smithsonian</t>
   </si>
   <si>
@@ -298,9 +286,6 @@
     <t>Yale Peabody Museum</t>
   </si>
   <si>
-    <t>Priority to nudge again to see if they are willing to contribute</t>
-  </si>
-  <si>
     <t xml:space="preserve">jtrimble@oeb.harvard.edu, jeremiah.trimble@gmail.com </t>
   </si>
   <si>
@@ -328,9 +313,6 @@
     <t>Maybe can nudge after a week, they mentioned they will start measuring from around the 20th</t>
   </si>
   <si>
-    <t>René Corado</t>
-  </si>
-  <si>
     <t>Abbreviation selected (if applicable)</t>
   </si>
   <si>
@@ -349,30 +331,15 @@
     <t xml:space="preserve">irham.mzb@gmail.com </t>
   </si>
   <si>
-    <t>Ross Crates</t>
-  </si>
-  <si>
-    <t>ANWC (Australian National Wildlife Collection)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ross.crates@anu.edu.au </t>
   </si>
   <si>
-    <t>Can nudge again to see if they found anyone who can help measure specimens at the collection</t>
-  </si>
-  <si>
     <t>TBRI (Taiwan Biodiversity Research Institute</t>
   </si>
   <si>
     <t xml:space="preserve">sychamore@gmail.com </t>
   </si>
   <si>
-    <t>Max Khoo &amp; Gabriel Low</t>
-  </si>
-  <si>
-    <t>Can wait for a response from Gabriel as to whether he can contribute with field data</t>
-  </si>
-  <si>
     <t>Field (Singapore)</t>
   </si>
   <si>
@@ -388,9 +355,6 @@
     <t>jaromeali@gmail.com</t>
   </si>
   <si>
-    <t>We just sent them the priority list, can wait for a response</t>
-  </si>
-  <si>
     <t xml:space="preserve">kalukapu@ualberta.ca </t>
   </si>
   <si>
@@ -451,9 +415,6 @@
     <t xml:space="preserve">chima.nwaogu@uct.ac.za </t>
   </si>
   <si>
-    <t>Priority to chase up regarding whether they were able to take any field measurements</t>
-  </si>
-  <si>
     <t>Saeed Abbas</t>
   </si>
   <si>
@@ -487,9 +448,6 @@
     <t xml:space="preserve">vgr7@cornell.edu </t>
   </si>
   <si>
-    <t>Just sent over the priority list, will wait for a few weeks before chasing up</t>
-  </si>
-  <si>
     <t>Y (28/04/2026</t>
   </si>
   <si>
@@ -502,27 +460,9 @@
     <t xml:space="preserve">cdingle@capilanou.ca </t>
   </si>
   <si>
-    <t>Still at the priority list stage, will start measuring once we send it across</t>
-  </si>
-  <si>
-    <t>Philip D. Round</t>
-  </si>
-  <si>
-    <t>Bangkok?</t>
-  </si>
-  <si>
     <t xml:space="preserve">pdround@ksc.th.co </t>
   </si>
   <si>
-    <t>Established contact again on 28th, said he will gain access and send data in a few weeks</t>
-  </si>
-  <si>
-    <t>Has some bulbul specimens in computer (NOT AVONET PROTOCOL), has forwarded contact of Thai museum curators</t>
-  </si>
-  <si>
-    <t>Mentioned on 29th that he would check for a list of holdings in about a week, will follow up</t>
-  </si>
-  <si>
     <t>Unable to provide specimens, too busy</t>
   </si>
   <si>
@@ -556,9 +496,6 @@
     <t>Camila Gibas Meneses, Kier Mitchel Pitogo</t>
   </si>
   <si>
-    <t xml:space="preserve">90 (field) &amp; 117 (NMP) </t>
-  </si>
-  <si>
     <t>Royal Belgian Institute for Natural Sciences (RBINS)</t>
   </si>
   <si>
@@ -571,9 +508,6 @@
     <t>Field Museum of Natural History (FMNH)</t>
   </si>
   <si>
-    <t>Now willing to contribute, priority list sent</t>
-  </si>
-  <si>
     <t>Already mentioned that preliminary specimens were measured, is sending new list</t>
   </si>
   <si>
@@ -595,56 +529,6 @@
     <t xml:space="preserve">jbates@fieldmuseum.org, shackett@fieldmuseum.org </t>
   </si>
   <si>
-    <t>Just emailed asking about Prigogine's and Sassi's greenbul specimens (as well as any others)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Just emailed asking about </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P.snouckaerti</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P.tympanistrigus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> specimens (as well as any others)</t>
-    </r>
-  </si>
-  <si>
     <t>Has completed the measuring, potentially more from Brian before June end</t>
   </si>
   <si>
@@ -663,9 +547,6 @@
     <t>JAT sent an email asking for bird banding data</t>
   </si>
   <si>
-    <t>Sent a priority list, he responded with a list of specimens he managed to get before the collections closed</t>
-  </si>
-  <si>
     <t xml:space="preserve">guillem@birdring.net </t>
   </si>
   <si>
@@ -678,7 +559,133 @@
     <t xml:space="preserve">mizan.rahmanzool@du.ac.bd </t>
   </si>
   <si>
-    <t>MMR responded saying he will send a preliminary dataset of 5 birds soon</t>
+    <t>Philip D. Round, Wachara Sanguansombat</t>
+  </si>
+  <si>
+    <t>NSM (National Science Museum), Thailand</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>~1000</t>
+  </si>
+  <si>
+    <t>Common bulbul measurements sent over</t>
+  </si>
+  <si>
+    <t>KU (Kansas University)</t>
+  </si>
+  <si>
+    <t>Robin Vijayan, Naman Goyal</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>IISER Tirupati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robin@labs.iisertirupati.ac.in, naman.goyal1992@gmail.com </t>
+  </si>
+  <si>
+    <t>Peter Njoroge</t>
+  </si>
+  <si>
+    <t>National Museums of Kenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pnjoroge@museums.or.ke </t>
+  </si>
+  <si>
+    <t>Peter just responded asking the way forward for data collection</t>
+  </si>
+  <si>
+    <t>RC, HB</t>
+  </si>
+  <si>
+    <t>René Corado, Hannah Batten</t>
+  </si>
+  <si>
+    <t>Just sent over their data of 30 specimens so far, unlikely to give more</t>
+  </si>
+  <si>
+    <t>KW</t>
+  </si>
+  <si>
+    <t>ANWC (Australian National Wildlife Collection) + MVIC Melbourne + Australian Museum (for Ross)</t>
+  </si>
+  <si>
+    <t>Ross sent his 2 bulbuls, more coming from Ricky-Lee, Lainie is measuring 6 specimens from MVIC</t>
+  </si>
+  <si>
+    <t>Ross Crates (AM), Ricky-Lee (AM), Lainie Berry (LB)</t>
+  </si>
+  <si>
+    <t>Data collection for bulbuls complete, but also add Jose Tchamba for Lubango data</t>
+  </si>
+  <si>
+    <t>90 (field), 117 (NMP), ~ 500 (Lubango)</t>
+  </si>
+  <si>
+    <t>Just sent a batch of field data to check</t>
+  </si>
+  <si>
+    <t>Malcolm Soh, Adham Ashton-Butt, Daniel Kong, Kelvin S.-H Peh (supervisor)</t>
+  </si>
+  <si>
+    <t>MCKS, AAB, DK</t>
+  </si>
+  <si>
+    <t>MMR</t>
+  </si>
+  <si>
+    <t>VGR</t>
+  </si>
+  <si>
+    <t>Remind just around 2nd week of June</t>
+  </si>
+  <si>
+    <t>Remind just around 1st week of June</t>
+  </si>
+  <si>
+    <t>ROC, LAB</t>
+  </si>
+  <si>
+    <t>MPJN</t>
+  </si>
+  <si>
+    <t>RIF</t>
+  </si>
+  <si>
+    <t>Sending around 100 specimens by last week of June</t>
+  </si>
+  <si>
+    <t>Naman got back with the field data</t>
+  </si>
+  <si>
+    <t>Remind in 2nd week of June</t>
+  </si>
+  <si>
+    <t>Got back with data, no need to remind</t>
+  </si>
+  <si>
+    <t>MMR has provided a preliminary dataset</t>
+  </si>
+  <si>
+    <t>Need to have a meeting 1st or 2nd week of June</t>
+  </si>
+  <si>
+    <t>Already sent back data</t>
+  </si>
+  <si>
+    <t>Has started measuring now</t>
+  </si>
+  <si>
+    <t>Measured one batch, is measuring another now</t>
+  </si>
+  <si>
+    <t>Has sent over the data</t>
   </si>
 </sst>
 </file>
@@ -721,15 +728,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -754,6 +758,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -768,7 +778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -789,6 +799,12 @@
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1104,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3A1E84-62D7-0B4D-AB6F-CC6222899977}">
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.6640625" customWidth="1"/>
@@ -1120,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1164,10 +1180,10 @@
         <v>10</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>12</v>
@@ -1185,7 +1201,7 @@
         <v>46140</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1202,7 +1218,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1240,7 +1256,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>11</v>
@@ -1275,10 +1291,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>11</v>
@@ -1296,7 +1312,7 @@
         <v>46141</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1307,13 +1323,13 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -1351,10 +1367,10 @@
         <v>31</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>12</v>
@@ -1389,10 +1405,10 @@
         <v>35</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>12</v>
@@ -1427,7 +1443,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -1448,42 +1464,42 @@
         <v>46132</v>
       </c>
       <c r="L9" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="3">
         <v>46122</v>
       </c>
-      <c r="L10" s="8" t="s">
-        <v>127</v>
+      <c r="L10" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -1500,10 +1516,10 @@
         <v>41</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>12</v>
@@ -1521,7 +1537,7 @@
         <v>46150</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1529,16 +1545,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
         <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -1553,13 +1569,13 @@
         <v>44</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="K12" s="1">
         <v>46113</v>
       </c>
       <c r="L12" t="s">
-        <v>45</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -1567,16 +1583,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>11</v>
@@ -1597,7 +1613,7 @@
         <v>46129</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1605,19 +1621,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" t="s">
         <v>60</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -1635,7 +1651,7 @@
         <v>46107</v>
       </c>
       <c r="L14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -1643,16 +1659,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>11</v>
@@ -1669,8 +1688,8 @@
       <c r="K15" s="10">
         <v>46111</v>
       </c>
-      <c r="L15" s="8" t="s">
-        <v>66</v>
+      <c r="L15" s="15" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -1678,16 +1697,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>11</v>
@@ -1708,7 +1727,7 @@
         <v>46119</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -1716,16 +1735,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -1746,7 +1765,7 @@
         <v>46133</v>
       </c>
       <c r="L17" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -1754,16 +1773,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -1784,7 +1803,7 @@
         <v>46125</v>
       </c>
       <c r="L18" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -1792,16 +1811,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>11</v>
@@ -1816,10 +1835,10 @@
         <v>24</v>
       </c>
       <c r="K19" s="10">
-        <v>46121</v>
+        <v>46175</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -1827,16 +1846,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>11</v>
@@ -1854,7 +1873,7 @@
         <v>46140</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -1862,16 +1881,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
@@ -1892,77 +1911,80 @@
         <v>46132</v>
       </c>
       <c r="L21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="8">
+        <v>30</v>
+      </c>
+      <c r="K22" s="10">
+        <v>46161</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11">
-        <v>21</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="D23" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="J22" s="11" t="s">
+      <c r="F23" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="13">
-        <v>46127</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="13">
-        <v>46132</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>96</v>
+      <c r="K23" s="23">
+        <v>46168</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -1970,16 +1992,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>104</v>
+        <v>194</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>11</v>
@@ -1994,10 +2019,10 @@
         <v>24</v>
       </c>
       <c r="K24" s="10">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>107</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2005,19 +2030,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>12</v>
@@ -2026,7 +2051,7 @@
         <v>11</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="J25" s="8">
         <v>72</v>
@@ -2035,42 +2060,45 @@
         <v>46140</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="J26" s="11" t="s">
+      <c r="B26" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="13">
-        <v>46139</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>111</v>
+      <c r="K26" s="16">
+        <v>46167</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -2078,13 +2106,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>11</v>
@@ -2104,8 +2132,8 @@
       <c r="K27" s="13">
         <v>46139</v>
       </c>
-      <c r="L27" s="11" t="s">
-        <v>117</v>
+      <c r="L27" s="18" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -2113,16 +2141,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>11</v>
@@ -2136,11 +2164,11 @@
       <c r="J28" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="13">
-        <v>46110</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>161</v>
+      <c r="K28" s="17">
+        <v>46164</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -2148,16 +2176,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>128</v>
+        <v>116</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>206</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>11</v>
@@ -2175,42 +2206,42 @@
         <v>46141</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="B30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="3">
         <v>46123</v>
       </c>
-      <c r="L30" s="8" t="s">
-        <v>134</v>
+      <c r="L30" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2218,17 +2249,17 @@
         <v>30</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E31" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>151</v>
-      </c>
       <c r="G31" s="8" t="s">
         <v>11</v>
       </c>
@@ -2236,51 +2267,51 @@
         <v>11</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J31" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K31" s="16">
+        <v>46160</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="10">
-        <v>46084</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>31</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K32" s="10">
+      <c r="K32" s="3">
         <v>46074</v>
       </c>
-      <c r="L32" s="8" t="s">
-        <v>142</v>
+      <c r="L32" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2288,16 +2319,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>11</v>
@@ -2308,14 +2339,14 @@
       <c r="I33" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="8" t="s">
-        <v>24</v>
+      <c r="J33" s="2">
+        <v>6</v>
       </c>
       <c r="K33" s="10">
         <v>46085</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -2323,13 +2354,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>134</v>
+      </c>
+      <c r="C34" t="s">
+        <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -2350,7 +2384,7 @@
         <v>46139</v>
       </c>
       <c r="L34" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -2358,13 +2392,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -2385,7 +2419,7 @@
         <v>46140</v>
       </c>
       <c r="L35" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -2393,13 +2427,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -2419,8 +2453,8 @@
       <c r="K36" s="1">
         <v>46140</v>
       </c>
-      <c r="L36" t="s">
-        <v>160</v>
+      <c r="L36" s="24" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -2428,13 +2462,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>163</v>
+        <v>143</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>11</v>
@@ -2452,45 +2489,45 @@
         <v>24</v>
       </c>
       <c r="K37" s="13">
-        <v>46153</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
+        <v>46170</v>
+      </c>
+      <c r="L37" s="25" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="11">
         <v>38</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J38" s="8" t="s">
+      <c r="B38" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="13">
         <v>46154</v>
       </c>
-      <c r="L38" s="8" t="s">
-        <v>186</v>
+      <c r="L38" s="18" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2498,13 +2535,13 @@
         <v>39</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>11</v>
@@ -2524,8 +2561,8 @@
       <c r="K39" s="10">
         <v>46154</v>
       </c>
-      <c r="L39" s="8" t="s">
-        <v>187</v>
+      <c r="L39" s="15" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2533,13 +2570,13 @@
         <v>40</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>11</v>
@@ -2560,7 +2597,7 @@
         <v>46149</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2568,13 +2605,13 @@
         <v>41</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>11</v>
@@ -2592,7 +2629,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2600,13 +2637,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>196</v>
+        <v>171</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>11</v>
@@ -2620,14 +2660,87 @@
       <c r="I42" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J42" s="8" t="s">
-        <v>24</v>
+      <c r="J42" s="2">
+        <v>5</v>
       </c>
       <c r="K42" s="10">
         <v>46155</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>199</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="8">
+        <v>43</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" s="8">
+        <v>357</v>
+      </c>
+      <c r="K43" s="10">
+        <v>46150</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="8">
+        <v>44</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" s="10">
+        <v>46161</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2669,6 +2782,8 @@
     <hyperlink ref="E40" r:id="rId35" display="jbates@fieldmuseum.org " xr:uid="{866767E7-7F87-6443-BB49-AC8BD2045175}"/>
     <hyperlink ref="E41" r:id="rId36" xr:uid="{81B825C4-58B8-914D-A03C-1DA829E3A96A}"/>
     <hyperlink ref="E42" r:id="rId37" xr:uid="{2C7B8AFC-6924-354A-8A18-106FEED63C02}"/>
+    <hyperlink ref="E43" r:id="rId38" display="robin@labs.iisertirupati.ac.in " xr:uid="{33783032-5947-0742-A748-4AFE5EDC2F4A}"/>
+    <hyperlink ref="E44" r:id="rId39" xr:uid="{984EA44A-088A-8E45-A532-3DAD103DC40E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Measurer_metadata_tracking.xlsx
+++ b/data/Measurer_metadata_tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B425DD5-9B72-BE44-B9E7-E453EBE659EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B2B97C-9CA9-A548-8387-8D45753DE959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="500" windowWidth="28040" windowHeight="15940" xr2:uid="{9CDA16BA-74DE-1D48-B98F-7FC82E70CC92}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="235">
   <si>
     <t>Sr. No</t>
   </si>
@@ -139,15 +139,6 @@
     <t>ROM (Royal Ontario Museum)</t>
   </si>
   <si>
-    <t>Liu Yang</t>
-  </si>
-  <si>
-    <t>LY</t>
-  </si>
-  <si>
-    <t>SYSU Guangzhou?</t>
-  </si>
-  <si>
     <t>Correspondence email address</t>
   </si>
   <si>
@@ -737,6 +728,18 @@
   </si>
   <si>
     <t>Wachara, Irham, TYY, Tharindu, Peter Njoroge, Orlando, Jarome (last)</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>Liu Yang &amp; Yue We</t>
+  </si>
+  <si>
+    <t>LY, YW</t>
+  </si>
+  <si>
+    <t>SYSU Guangzhou &amp; Chinese Academy of Sciences</t>
   </si>
 </sst>
 </file>
@@ -1192,13 +1195,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>5</v>
@@ -1227,19 +1230,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>10</v>
@@ -1257,7 +1260,7 @@
         <v>46188</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1274,7 +1277,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
@@ -1312,7 +1315,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>9</v>
@@ -1347,10 +1350,10 @@
         <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>9</v>
@@ -1368,7 +1371,7 @@
         <v>46141</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1379,16 +1382,16 @@
         <v>24</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>10</v>
@@ -1406,7 +1409,7 @@
         <v>46182</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1423,10 +1426,10 @@
         <v>28</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>10</v>
@@ -1444,7 +1447,7 @@
         <v>46178</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1452,7 +1455,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>29</v>
@@ -1461,10 +1464,10 @@
         <v>30</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>10</v>
@@ -1482,7 +1485,7 @@
         <v>46175</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1499,7 +1502,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>9</v>
@@ -1520,7 +1523,7 @@
         <v>46132</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -1528,16 +1531,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>9</v>
@@ -1555,7 +1558,7 @@
         <v>46177</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1563,19 +1566,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>34</v>
+        <v>232</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>36</v>
+        <v>234</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>10</v>
@@ -1593,7 +1596,7 @@
         <v>46178</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1601,16 +1604,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>9</v>
@@ -1625,13 +1628,13 @@
         <v>10</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K12" s="6">
         <v>46113</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1639,19 +1642,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>10</v>
@@ -1669,7 +1672,7 @@
         <v>46188</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1677,19 +1680,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>10</v>
@@ -1715,19 +1718,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="E15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>10</v>
@@ -1745,7 +1748,7 @@
         <v>46184</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1753,19 +1756,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>10</v>
@@ -1783,7 +1786,7 @@
         <v>46188</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1791,16 +1794,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>9</v>
@@ -1821,7 +1824,7 @@
         <v>46133</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1829,19 +1832,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>10</v>
@@ -1859,7 +1862,7 @@
         <v>46177</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1867,16 +1870,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>9</v>
@@ -1894,7 +1897,7 @@
         <v>46175</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1902,16 +1905,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>9</v>
@@ -1929,7 +1932,7 @@
         <v>46140</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -1937,19 +1940,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>10</v>
@@ -1967,7 +1970,7 @@
         <v>46188</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1975,16 +1978,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>9</v>
@@ -2005,7 +2008,7 @@
         <v>46161</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -2013,16 +2016,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G23" s="15" t="s">
         <v>9</v>
@@ -2040,7 +2043,7 @@
         <v>46188</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -2048,19 +2051,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>10</v>
@@ -2078,7 +2081,7 @@
         <v>46169</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2086,19 +2089,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>10</v>
@@ -2116,7 +2119,7 @@
         <v>46140</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2124,16 +2127,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>9</v>
@@ -2154,7 +2157,7 @@
         <v>46167</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -2162,13 +2165,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>9</v>
@@ -2189,7 +2192,7 @@
         <v>46139</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -2197,16 +2200,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>9</v>
@@ -2224,7 +2230,7 @@
         <v>46164</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2232,19 +2238,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>10</v>
@@ -2262,7 +2268,7 @@
         <v>46141</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -2270,16 +2276,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>9</v>
@@ -2297,7 +2303,7 @@
         <v>46188</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2305,19 +2311,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>9</v>
@@ -2335,7 +2341,7 @@
         <v>46160</v>
       </c>
       <c r="L31" s="20" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -2343,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>9</v>
@@ -2370,7 +2376,7 @@
         <v>46188</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -2378,16 +2384,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G33" s="15" t="s">
         <v>9</v>
@@ -2405,7 +2411,7 @@
         <v>46186</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2413,16 +2419,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>9</v>
@@ -2443,7 +2449,7 @@
         <v>46168</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2451,19 +2457,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>10</v>
@@ -2481,7 +2487,7 @@
         <v>46188</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2489,19 +2495,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>9</v>
@@ -2513,13 +2519,13 @@
         <v>9</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K36" s="12">
         <v>46189</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2527,16 +2533,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>9</v>
@@ -2557,7 +2563,7 @@
         <v>46170</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -2565,16 +2571,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>9</v>
@@ -2595,7 +2601,7 @@
         <v>46186</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -2603,13 +2609,13 @@
         <v>39</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>9</v>
@@ -2630,7 +2636,7 @@
         <v>46188</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -2638,13 +2644,13 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>9</v>
@@ -2665,7 +2671,7 @@
         <v>46149</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -2673,13 +2679,13 @@
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>9</v>
@@ -2700,7 +2706,7 @@
         <v>46153</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -2708,16 +2714,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>9</v>
@@ -2738,7 +2744,7 @@
         <v>46167</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2746,16 +2752,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>9</v>
@@ -2776,7 +2782,7 @@
         <v>46150</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -2784,13 +2790,13 @@
         <v>44</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>9</v>
@@ -2811,7 +2817,7 @@
         <v>46176</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -2819,13 +2825,13 @@
         <v>45</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>22</v>
@@ -2849,15 +2855,15 @@
         <v>46181</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
